--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:19</t>
+    <t xml:space="preserve">2026-10-05 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -756,7 +756,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1610132.62</v>
+        <v>1610132.63</v>
       </c>
     </row>
     <row r="10">
@@ -807,7 +807,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1316628.62</v>
+        <v>1316628.63</v>
       </c>
     </row>
     <row r="13">
@@ -824,7 +824,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1295339.62</v>
+        <v>1295339.63</v>
       </c>
     </row>
     <row r="14">
@@ -960,7 +960,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1214878.62</v>
+        <v>1214878.63</v>
       </c>
     </row>
     <row r="22">
@@ -977,7 +977,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1210872.62</v>
+        <v>1210872.63</v>
       </c>
     </row>
     <row r="23">
@@ -1028,7 +1028,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1166510.12</v>
+        <v>1166510.13</v>
       </c>
     </row>
     <row r="26">
@@ -1130,7 +1130,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1091208.62</v>
+        <v>1091208.63</v>
       </c>
     </row>
     <row r="32">
@@ -1249,7 +1249,7 @@
         <v>2023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>990222.12</v>
+        <v>990222.13</v>
       </c>
     </row>
     <row r="39">
@@ -1402,7 +1402,7 @@
         <v>2023</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>920077.12</v>
+        <v>920077.13</v>
       </c>
     </row>
     <row r="48">
@@ -1470,7 +1470,7 @@
         <v>2023</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>851082.12</v>
+        <v>851082.13</v>
       </c>
     </row>
     <row r="52">
@@ -1487,7 +1487,7 @@
         <v>2023</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>848047.62</v>
+        <v>848047.63</v>
       </c>
     </row>
     <row r="53">
